--- a/backend/src/data/demo_bookings.xlsx
+++ b/backend/src/data/demo_bookings.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <cols>
     <col min="1" max="1" width="24.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -695,9 +695,35 @@
         <v>New Demo Booking</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>9/9/2026, 8:40:46 am IST</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Aa</v>
+      </c>
+      <c r="C12" t="str">
+        <v>aa@gmail.com</v>
+      </c>
+      <c r="D12" t="str">
+        <v>123456789</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Data Analytics with SQL, Power BI, Python, Excel</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Immediate</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Flexible</v>
+      </c>
+      <c r="H12" t="str">
+        <v>New Demo Booking</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/src/data/demo_bookings.xlsx
+++ b/backend/src/data/demo_bookings.xlsx
@@ -397,16 +397,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:I13"/>
   <cols>
     <col min="1" max="1" width="24.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
     <col min="3" max="3" width="28.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
     <col min="5" max="5" width="45.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -434,6 +433,9 @@
       <c r="H1" t="str">
         <v>Status</v>
       </c>
+      <c r="I1" t="str">
+        <v>Referral</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -721,9 +723,32 @@
         <v>New Demo Booking</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>9/9/2026, 10:00:11 pm IST</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Abhi</v>
+      </c>
+      <c r="C13" t="str">
+        <v>abhi@gmail.com</v>
+      </c>
+      <c r="D13" t="str">
+        <v>9100449157</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Data Analytics with SQL, Power BI, Python, Excel</v>
+      </c>
+      <c r="H13" t="str">
+        <v>New Demo Booking</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Mahesh</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I13"/>
   </ignoredErrors>
 </worksheet>
 </file>